--- a/relatorio_final_agosto.xlsx
+++ b/relatorio_final_agosto.xlsx
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>225.0734050179211</v>
+        <v>210.6395161290322</v>
       </c>
       <c r="C5" t="n">
-        <v>-11.03039426523297</v>
+        <v>-10.21854838709677</v>
       </c>
     </row>
     <row r="6">
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1152</v>
+        <v>1679</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>-78</v>
+        <v>-81</v>
       </c>
     </row>
   </sheetData>
